--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487783_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487783_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. NDIAYE</t>
+          <t>J. BLACK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9195</v>
+        <v>6.0928</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1771</v>
+        <v>3.7962</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7423999999999999</v>
+        <v>2.2966</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4296</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0148</v>
+        <v>2.1727</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4149</v>
+        <v>-1.5855</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8012</v>
+        <v>-0.0047</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9292</v>
+        <v>2.2258</v>
       </c>
       <c r="L2" t="n">
-        <v>1.872</v>
+        <v>-2.2305</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3716</v>
+        <v>0.5918</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0856</v>
+        <v>-0.0532</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4572</v>
+        <v>0.645</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1974</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>2.789</v>
+        <v>0.882</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4085</v>
+        <v>0.0398</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4599</v>
+        <v>2.9188</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6275</v>
+        <v>2.9188</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. BLACK</t>
+          <t>S. NDIAYE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1046</v>
+        <v>5.9319</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3676</v>
+        <v>5.2482</v>
       </c>
       <c r="F3" t="n">
-        <v>2.737</v>
+        <v>0.6837</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5872000000000001</v>
+        <v>3.4296</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1727</v>
+        <v>2.0148</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.5855</v>
+        <v>1.4149</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0047</v>
+        <v>3.8012</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2258</v>
+        <v>1.9292</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.2305</v>
+        <v>1.872</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5918</v>
+        <v>-0.3716</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0532</v>
+        <v>0.0856</v>
       </c>
       <c r="O3" t="n">
-        <v>0.645</v>
+        <v>-0.4572</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9336</v>
+        <v>1.2099</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4534</v>
+        <v>0.8601</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4802</v>
+        <v>0.3498</v>
       </c>
       <c r="V3" t="n">
-        <v>2.9188</v>
+        <v>0.4599</v>
       </c>
       <c r="W3" t="n">
-        <v>2.9188</v>
+        <v>1.6275</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2036</v>
+        <v>5.8186</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3825</v>
+        <v>2.704</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8211</v>
+        <v>3.1147</v>
       </c>
       <c r="G4" t="n">
         <v>3.9274</v>
@@ -766,13 +766,13 @@
         <v>1.2487</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1305</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3229</v>
+        <v>0.6444</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1924</v>
+        <v>0.1012</v>
       </c>
       <c r="V4" t="n">
         <v>0.9376</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8814</v>
+        <v>4.0751</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3243</v>
+        <v>2.7529</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5571</v>
+        <v>1.3222</v>
       </c>
       <c r="G5" t="n">
         <v>1.3517</v>
@@ -844,13 +844,13 @@
         <v>1.8731</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4058</v>
+        <v>0.5996</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2577</v>
+        <v>0.6863</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1482</v>
+        <v>-0.0867</v>
       </c>
       <c r="V5" t="n">
         <v>1.2914</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4714</v>
+        <v>3.5404</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4708</v>
+        <v>2.3636</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0007</v>
+        <v>1.1768</v>
       </c>
       <c r="G6" t="n">
         <v>2.8082</v>
@@ -922,13 +922,13 @@
         <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2075</v>
+        <v>0.2765</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1338</v>
+        <v>-0.2409</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3412</v>
+        <v>0.5174</v>
       </c>
       <c r="V6" t="n">
         <v>0.2477</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2576</v>
+        <v>1.8671</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3111</v>
+        <v>1.0968</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9465</v>
+        <v>0.7703</v>
       </c>
       <c r="G7" t="n">
         <v>0.8198</v>
@@ -1000,13 +1000,13 @@
         <v>1.0406</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8331</v>
+        <v>0.4427</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2577</v>
+        <v>0.0434</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5755</v>
+        <v>0.3993</v>
       </c>
       <c r="V7" t="n">
         <v>1.6452</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. BELLO MOURE</t>
+          <t>G. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5488</v>
+        <v>1.3124</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0751</v>
+        <v>-0.0416</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4738</v>
+        <v>1.3539</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3466</v>
+        <v>1.1956</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3285</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6752</v>
+        <v>1.1038</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0486</v>
+        <v>0.5099</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0959</v>
+        <v>0.4797</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1445</v>
+        <v>0.0302</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2981</v>
+        <v>0.6857</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2326</v>
+        <v>-0.3879</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5306999999999999</v>
+        <v>1.0736</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6041</v>
+        <v>0.4924</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0033</v>
+        <v>0.4891</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.0033</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7076</v>
+        <v>-0.5838</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4599</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. OROZCO DOMINGUEZ</t>
+          <t>A. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3274</v>
+        <v>0.5268</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7917</v>
+        <v>-1.0792</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1191</v>
+        <v>1.606</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1956</v>
+        <v>1.1629</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09180000000000001</v>
+        <v>-1.1492</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1038</v>
+        <v>2.3121</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5099</v>
+        <v>0.3343</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4797</v>
+        <v>-1.3328</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0302</v>
+        <v>1.6671</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6857</v>
+        <v>0.8286</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3879</v>
+        <v>0.1836</v>
       </c>
       <c r="O9" t="n">
-        <v>1.0736</v>
+        <v>0.645</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2081</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4925</v>
+        <v>0.0101</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.261</v>
+        <v>-0.3729</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2316</v>
+        <v>0.383</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5838</v>
+        <v>-0.23</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5838</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. OROZCO DOMINGUEZ</t>
+          <t>F. BELLO MOURE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.107</v>
+        <v>0.3742</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2935</v>
+        <v>-0.2464</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4004</v>
+        <v>0.6206</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1629</v>
+        <v>-0.3466</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1492</v>
+        <v>0.3285</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3121</v>
+        <v>-0.6752</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3343</v>
+        <v>-0.0486</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3328</v>
+        <v>0.0959</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6671</v>
+        <v>-0.1445</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8286</v>
+        <v>-0.2981</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1836</v>
+        <v>0.2326</v>
       </c>
       <c r="O10" t="n">
-        <v>0.645</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="P10" t="n">
         <v>-0.4162</v>
@@ -1234,22 +1234,22 @@
         <v>0.6244</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4097</v>
+        <v>0.4294</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.3248</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1775</v>
+        <v>0.7542</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.23</v>
+        <v>0.7076</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.23</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0489</v>
+        <v>-0.2544</v>
       </c>
       <c r="E11" t="n">
         <v>-0.5682</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5194</v>
+        <v>0.3139</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4708</v>
@@ -1312,13 +1312,13 @@
         <v>0.2081</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0463</v>
+        <v>-0.1592</v>
       </c>
       <c r="T11" t="n">
         <v>-0.3262</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3725</v>
+        <v>0.167</v>
       </c>
       <c r="V11" t="n">
         <v>1.1675</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0388</v>
+        <v>-0.7452</v>
       </c>
       <c r="E12" t="n">
         <v>-0.5036</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5352</v>
+        <v>-0.2416</v>
       </c>
       <c r="G12" t="n">
         <v>-2.5697</v>
@@ -1390,13 +1390,13 @@
         <v>0.6244</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.261</v>
+        <v>0.0326</v>
       </c>
       <c r="T12" t="n">
         <v>-0.4567</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1957</v>
+        <v>0.4893</v>
       </c>
       <c r="V12" t="n">
         <v>1.1675</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.2043</v>
+        <v>-1.0106</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.5642</v>
+        <v>-1.1356</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3599</v>
+        <v>0.125</v>
       </c>
       <c r="G13" t="n">
         <v>-1.8525</v>
@@ -1468,13 +1468,13 @@
         <v>1.2487</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2101</v>
+        <v>0.4038</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6524</v>
+        <v>-0.2238</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8625</v>
+        <v>0.6277</v>
       </c>
       <c r="V13" t="n">
         <v>0.23</v>
@@ -1501,28 +1501,28 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>27.5293</v>
+        <v>27.5291</v>
       </c>
       <c r="E14" t="n">
-        <v>14.3873</v>
+        <v>14.3871</v>
       </c>
       <c r="F14" t="n">
-        <v>13.1422</v>
+        <v>13.1421</v>
       </c>
       <c r="G14" t="n">
         <v>9.0428</v>
       </c>
       <c r="H14" t="n">
-        <v>8.858999999999998</v>
+        <v>8.859</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1836000000000002</v>
+        <v>0.1835999999999993</v>
       </c>
       <c r="J14" t="n">
         <v>9.370100000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>7.982499999999999</v>
+        <v>7.982500000000001</v>
       </c>
       <c r="L14" t="n">
         <v>1.3878</v>
@@ -1546,13 +1546,13 @@
         <v>13.5278</v>
       </c>
       <c r="S14" t="n">
-        <v>5.405199999999999</v>
+        <v>5.405200000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>1.660099999999999</v>
+        <v>1.659999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>3.7452</v>
+        <v>3.7453</v>
       </c>
       <c r="V14" t="n">
         <v>9.9594</v>
@@ -1561,7 +1561,7 @@
         <v>13.7627</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.803199999999999</v>
+        <v>-3.8032</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7035</v>
+        <v>4.4114</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7523</v>
+        <v>4.4308</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0488</v>
+        <v>-0.0194</v>
       </c>
       <c r="G15" t="n">
         <v>2.1269</v>
@@ -1624,13 +1624,13 @@
         <v>0.4162</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5258</v>
+        <v>0.2337</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3229</v>
+        <v>0.0014</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2029</v>
+        <v>0.2323</v>
       </c>
       <c r="V15" t="n">
         <v>1.6345</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0188</v>
+        <v>0.0311</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6676</v>
+        <v>-0.8819</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.913</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9341</v>
@@ -1702,13 +1702,13 @@
         <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3334</v>
+        <v>-0.2835</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2643</v>
+        <v>-0.4786</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.06909999999999999</v>
+        <v>0.1951</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5681</v>
+        <v>-0.5784</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0473</v>
+        <v>0.0598</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5208</v>
+        <v>-0.6382</v>
       </c>
       <c r="G17" t="n">
         <v>1.8735</v>
@@ -1780,13 +1780,13 @@
         <v>1.0406</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2336</v>
+        <v>-0.2438</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1338</v>
+        <v>-0.0266</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0998</v>
+        <v>-0.2172</v>
       </c>
       <c r="V17" t="n">
         <v>-1.1675</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7603</v>
+        <v>-0.615</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0504</v>
+        <v>0.271</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7099</v>
+        <v>-0.8861</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4086</v>
@@ -1858,13 +1858,13 @@
         <v>1.4568</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7542</v>
+        <v>-0.6089</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3701</v>
+        <v>-1.0486</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6159</v>
+        <v>0.4398</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0543</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1283</v>
+        <v>-0.9815</v>
       </c>
       <c r="E19" t="n">
         <v>-0.148</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9802</v>
+        <v>-0.8334</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2227</v>
@@ -1936,13 +1936,13 @@
         <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1137</v>
+        <v>-0.9669</v>
       </c>
       <c r="T19" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0451</v>
+        <v>-0.8983</v>
       </c>
       <c r="V19" t="n">
         <v>0.5838</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8039</v>
+        <v>-1.4912</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8247</v>
+        <v>-0.7175</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9792</v>
+        <v>-0.7737000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5091</v>
@@ -2014,13 +2014,13 @@
         <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7359</v>
+        <v>-0.4233</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.48</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1487</v>
+        <v>0.0568</v>
       </c>
       <c r="V20" t="n">
         <v>0.6899</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0603</v>
+        <v>-2.9135</v>
       </c>
       <c r="E21" t="n">
         <v>-2.6149</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4455</v>
+        <v>-0.2987</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0771</v>
@@ -2092,13 +2092,13 @@
         <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7751</v>
+        <v>-0.6283</v>
       </c>
       <c r="T21" t="n">
         <v>0.1272</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9023</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.424</v>
+        <v>-4.9176</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7362</v>
+        <v>-3.2005</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6878</v>
+        <v>-1.7171</v>
       </c>
       <c r="G22" t="n">
         <v>0.09470000000000001</v>
@@ -2170,13 +2170,13 @@
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5416</v>
+        <v>-1.0352</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1744</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3673</v>
+        <v>-0.3966</v>
       </c>
       <c r="V22" t="n">
         <v>-2.9365</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7308</v>
+        <v>-5.8761</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1998</v>
+        <v>-1.5212</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.531</v>
+        <v>-4.3548</v>
       </c>
       <c r="G23" t="n">
         <v>-3.8152</v>
@@ -2248,13 +2248,13 @@
         <v>0.8325</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6531</v>
+        <v>-0.7984</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.199</v>
+        <v>-0.5205</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4541</v>
+        <v>-0.2779</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0543</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.0622</v>
+        <v>-6.9488</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.458</v>
+        <v>-3.3152</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.6042</v>
+        <v>-3.6336</v>
       </c>
       <c r="G24" t="n">
         <v>-0.0255</v>
@@ -2326,13 +2326,13 @@
         <v>0.6244</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4338</v>
+        <v>-0.4528</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8416</v>
+        <v>-0.0157</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4077</v>
+        <v>-0.4371</v>
       </c>
       <c r="V24" t="n">
         <v>-3.9731</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.6759</v>
+        <v>-7.6495</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.1475</v>
+        <v>-5.5045</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5285</v>
+        <v>-2.145</v>
       </c>
       <c r="G25" t="n">
         <v>-4.1454</v>
@@ -2404,13 +2404,13 @@
         <v>1.4568</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2244</v>
+        <v>-0.198</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2396</v>
+        <v>-0.5967</v>
       </c>
       <c r="U25" t="n">
-        <v>1.0152</v>
+        <v>0.3987</v>
       </c>
       <c r="V25" t="n">
         <v>-2.6818</v>
@@ -2443,7 +2443,7 @@
         <v>-13.1421</v>
       </c>
       <c r="F26" t="n">
-        <v>-14.3872</v>
+        <v>-14.387</v>
       </c>
       <c r="G26" t="n">
         <v>-9.0426</v>
@@ -2488,7 +2488,7 @@
         <v>-3.7452</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.6601</v>
+        <v>-1.6599</v>
       </c>
       <c r="V26" t="n">
         <v>-9.959299999999999</v>
